--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -30,7 +30,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.inera.se/ig/template/StructureDefinition/IneraPatient</t>
+    <t>https://anetteg-j.github.io/Testmall/StructureDefinition/IneraPatient</t>
   </si>
   <si>
     <t>Identifier</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -30,7 +30,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://anetteg-j.github.io/Testmall/StructureDefinition/IneraPatient</t>
+    <t>https://fhir.inera.se/ig/template/StructureDefinition/IneraPatient</t>
   </si>
   <si>
     <t>Identifier</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -30,7 +30,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.inera.se/ig/template/StructureDefinition/IneraPatient</t>
+    <t>https://pub.regionstockholm.se/fhir/StructureDefinition/Testmall/StructureDefinition/IneraPatient</t>
   </si>
   <si>
     <t>Identifier</t>
@@ -69,13 +69,13 @@
     <t>Publisher</t>
   </si>
   <si>
-    <t>Inera AB</t>
+    <t>Region Stockholm</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Inera AB (https://www.inera.se)</t>
+    <t>Region Stockholm (https://www.regionstockholm.se)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -30,7 +30,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://pub.regionstockholm.se/fhir/StructureDefinition/Testmall/StructureDefinition/IneraPatient</t>
+    <t>https://pub.regionstockholm.se/fhir/ImplementationGuide/Testmall/StructureDefinition/IneraPatient</t>
   </si>
   <si>
     <t>Identifier</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2599" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4788" uniqueCount="666">
   <si>
     <t>Property</t>
   </si>
@@ -1476,6 +1476,623 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/link-type|4.0.1</t>
+  </si>
+  <si>
+    <t>stockholm-genomic-device</t>
+  </si>
+  <si>
+    <t>https://pub.regionstockholm.se/fhir/ImplementationGuide/Testmall/StructureDefinition/stockholm-genomic-device</t>
+  </si>
+  <si>
+    <t>StockholmGenomicDevice</t>
+  </si>
+  <si>
+    <t>Stockholm Device</t>
+  </si>
+  <si>
+    <t>2026-10-29T10:49:58+00:00</t>
+  </si>
+  <si>
+    <t>Profile for devices and software systems used in genomic workflows, including sequencing platforms and bioinformatics pipelines referenced by procedures and analyses.</t>
+  </si>
+  <si>
+    <t>The purpose of this device profile is to store structured information about devices used to perform the Genomic Test</t>
+  </si>
+  <si>
+    <t>Device</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/Device</t>
+  </si>
+  <si>
+    <t>Item used in healthcare</t>
+  </si>
+  <si>
+    <t>A type of a manufactured item that is used in the provision of healthcare without being substantially changed through that activity. The device may be a medical or non-medical device.</t>
+  </si>
+  <si>
+    <t>Device.id</t>
+  </si>
+  <si>
+    <t>Device.meta</t>
+  </si>
+  <si>
+    <t>Device.implicitRules</t>
+  </si>
+  <si>
+    <t>Device.language</t>
+  </si>
+  <si>
+    <t>Device.text</t>
+  </si>
+  <si>
+    <t>Device.contained</t>
+  </si>
+  <si>
+    <t>Device.extension</t>
+  </si>
+  <si>
+    <t>Device.modifierExtension</t>
+  </si>
+  <si>
+    <t>Device.identifier</t>
+  </si>
+  <si>
+    <t>Business identifiers for the device or software</t>
+  </si>
+  <si>
+    <t>Identifiers that uniquely identify a physical device or analytical system in the local ecosystem.</t>
+  </si>
+  <si>
+    <t>The barcode string from a barcode present on a device label or package may identify the instance, include names given to the device in local usage, or may identify the type of device. If the identifier identifies the type of device, Device.type element should be used.</t>
+  </si>
+  <si>
+    <t>Device.definition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(DeviceDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>The reference to the definition for the device</t>
+  </si>
+  <si>
+    <t>The reference to the definition for the device.</t>
+  </si>
+  <si>
+    <t>Device.udiCarrier</t>
+  </si>
+  <si>
+    <t>Unique Device Identifier (UDI) Barcode string</t>
+  </si>
+  <si>
+    <t>Unique device identifier (UDI) assigned to device label or package.  Note that the Device may include multiple udiCarriers as it either may include just the udiCarrier for the jurisdiction it is sold, or for multiple jurisdictions it could have been sold.</t>
+  </si>
+  <si>
+    <t>UDI may identify an unique instance of a device, or it may only identify the type of the device.  See [UDI mappings](http://hl7.org/fhir/R4/device-mappings.html#udi) for a complete mapping of UDI parts to Device.</t>
+  </si>
+  <si>
+    <t>Device.udiCarrier.id</t>
+  </si>
+  <si>
+    <t>Device.udiCarrier.extension</t>
+  </si>
+  <si>
+    <t>Device.udiCarrier.modifierExtension</t>
+  </si>
+  <si>
+    <t>Device.udiCarrier.deviceIdentifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DI
+</t>
+  </si>
+  <si>
+    <t>Mandatory fixed portion of UDI</t>
+  </si>
+  <si>
+    <t>The device identifier (DI) is a mandatory, fixed portion of a UDI that identifies the labeler and the specific version or model of a device.</t>
+  </si>
+  <si>
+    <t>Device.udiCarrier.issuer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barcode System
+</t>
+  </si>
+  <si>
+    <t>UDI Issuing Organization</t>
+  </si>
+  <si>
+    <t>Organization that is charged with issuing UDIs for devices.  For example, the US FDA issuers include :
+1) GS1: 
+http://hl7.org/fhir/NamingSystem/gs1-di, 
+2) HIBCC:
+http://hl7.org/fhir/NamingSystem/hibcc-dI, 
+3) ICCBBA for blood containers:
+http://hl7.org/fhir/NamingSystem/iccbba-blood-di, 
+4) ICCBA for other devices:
+http://hl7.org/fhir/NamingSystem/iccbba-other-di.</t>
+  </si>
+  <si>
+    <t>Device.udiCarrier.jurisdiction</t>
+  </si>
+  <si>
+    <t>Regional UDI authority</t>
+  </si>
+  <si>
+    <t>The identity of the authoritative source for UDI generation within a  jurisdiction.  All UDIs are globally unique within a single namespace with the appropriate repository uri as the system.  For example,  UDIs of devices managed in the U.S. by the FDA, the value is  http://hl7.org/fhir/NamingSystem/fda-udi.</t>
+  </si>
+  <si>
+    <t>Allows a recipient of a UDI to know which database will contain the UDI-associated metadata.</t>
+  </si>
+  <si>
+    <t>Device.udiCarrier.carrierAIDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automatic Identification and Data Capture
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base64Binary
+</t>
+  </si>
+  <si>
+    <t>UDI Machine Readable Barcode String</t>
+  </si>
+  <si>
+    <t>The full UDI carrier of the Automatic Identification and Data Capture (AIDC) technology representation of the barcode string as printed on the packaging of the device - e.g., a barcode or RFID.   Because of limitations on character sets in XML and the need to round-trip JSON data through XML, AIDC Formats *SHALL* be base64 encoded.</t>
+  </si>
+  <si>
+    <t>The AIDC form of UDIs should be scanned or otherwise used for the identification of the device whenever possible to minimize errors in records resulting from manual transcriptions. If separate barcodes for DI and PI are present, concatenate the string with DI first and in order of human readable expression on label.</t>
+  </si>
+  <si>
+    <t>Device.udiCarrier.carrierHRF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human Readable Form
+</t>
+  </si>
+  <si>
+    <t>UDI Human Readable Barcode String</t>
+  </si>
+  <si>
+    <t>The full UDI carrier as the human readable form (HRF) representation of the barcode string as printed on the packaging of the device.</t>
+  </si>
+  <si>
+    <t>If separate barcodes for DI and PI are present, concatenate the string with DI first and in order of human readable expression on label.</t>
+  </si>
+  <si>
+    <t>Device.udiCarrier.entryType</t>
+  </si>
+  <si>
+    <t>barcode | rfid | manual +</t>
+  </si>
+  <si>
+    <t>A coded entry to indicate how the data was entered.</t>
+  </si>
+  <si>
+    <t>Supports a way to distinguish hand entered from machine read data.</t>
+  </si>
+  <si>
+    <t>Codes to identify how UDI data was entered.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/udi-entry-type|4.0.1</t>
+  </si>
+  <si>
+    <t>Device.status</t>
+  </si>
+  <si>
+    <t>Operational device status</t>
+  </si>
+  <si>
+    <t>Indicates whether the device is active, inactive, or entered in error at the time of use.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because the status contains the codes inactive and entered-in-error that mark the device (record)as not currently valid.</t>
+  </si>
+  <si>
+    <t>The availability status of the device.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/device-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Device.statusReason</t>
+  </si>
+  <si>
+    <t>online | paused | standby | offline | not-ready | transduc-discon | hw-discon | off</t>
+  </si>
+  <si>
+    <t>Reason for the dtatus of the Device availability.</t>
+  </si>
+  <si>
+    <t>The availability status reason of the device.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/device-status-reason|4.0.1</t>
+  </si>
+  <si>
+    <t>Device.distinctIdentifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distinct Identification Code (DIC)
+</t>
+  </si>
+  <si>
+    <t>The distinct identification string</t>
+  </si>
+  <si>
+    <t>The distinct identification string as required by regulation for a human cell, tissue, or cellular and tissue-based product.</t>
+  </si>
+  <si>
+    <t>For example, this applies to devices in the United States regulated under *Code of Federal Regulation 21CFR§1271.290(c)*.</t>
+  </si>
+  <si>
+    <t>Device.manufacturer</t>
+  </si>
+  <si>
+    <t>Name of device manufacturer</t>
+  </si>
+  <si>
+    <t>A name of the manufacturer.</t>
+  </si>
+  <si>
+    <t>Device.manufactureDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date when the device was made</t>
+  </si>
+  <si>
+    <t>The date and time when the device was manufactured.</t>
+  </si>
+  <si>
+    <t>Device.expirationDate</t>
+  </si>
+  <si>
+    <t>Date and time of expiry of this device (if applicable)</t>
+  </si>
+  <si>
+    <t>The date and time beyond which this device is no longer valid or should not be used (if applicable).</t>
+  </si>
+  <si>
+    <t>Device.lotNumber</t>
+  </si>
+  <si>
+    <t>Lot number of manufacture</t>
+  </si>
+  <si>
+    <t>Lot number assigned by the manufacturer.</t>
+  </si>
+  <si>
+    <t>Device.serialNumber</t>
+  </si>
+  <si>
+    <t>Serial number assigned by the manufacturer</t>
+  </si>
+  <si>
+    <t>The serial number assigned by the organization when the device was manufactured.</t>
+  </si>
+  <si>
+    <t>Alphanumeric Maximum 20.</t>
+  </si>
+  <si>
+    <t>Device.deviceName</t>
+  </si>
+  <si>
+    <t>The name of the device as given by the manufacturer</t>
+  </si>
+  <si>
+    <t>This represents the manufacturer's name of the device as provided by the device, from a UDI label, or by a person describing the Device.  This typically would be used when a person provides the name(s) or when the device represents one of the names available from DeviceDefinition.</t>
+  </si>
+  <si>
+    <t>Device.deviceName.id</t>
+  </si>
+  <si>
+    <t>Device.deviceName.extension</t>
+  </si>
+  <si>
+    <t>Device.deviceName.modifierExtension</t>
+  </si>
+  <si>
+    <t>Device.deviceName.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Σ
+</t>
+  </si>
+  <si>
+    <t>The name of the device</t>
+  </si>
+  <si>
+    <t>The name of the device.</t>
+  </si>
+  <si>
+    <t>Device.deviceName.type</t>
+  </si>
+  <si>
+    <t>udi-label-name | user-friendly-name | patient-reported-name | manufacturer-name | model-name | other</t>
+  </si>
+  <si>
+    <t>The type of deviceName.
+UDILabelName | UserFriendlyName | PatientReportedName | ManufactureDeviceName | ModelName.</t>
+  </si>
+  <si>
+    <t>The type of name the device is referred by.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/device-nametype|4.0.1</t>
+  </si>
+  <si>
+    <t>Device.modelNumber</t>
+  </si>
+  <si>
+    <t>The model number for the device</t>
+  </si>
+  <si>
+    <t>The model number for the device.</t>
+  </si>
+  <si>
+    <t>Device.partNumber</t>
+  </si>
+  <si>
+    <t>The part number of the device</t>
+  </si>
+  <si>
+    <t>The part number of the device.</t>
+  </si>
+  <si>
+    <t>Device.type</t>
+  </si>
+  <si>
+    <t>Classified device type used in genomics</t>
+  </si>
+  <si>
+    <t>Coded device type describing the platform, instrument, or software category used in the workflow.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes to identify medical devices.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/device-type|4.0.1</t>
+  </si>
+  <si>
+    <t>Device.specialization</t>
+  </si>
+  <si>
+    <t>The capabilities supported on a  device, the standards to which the device conforms for a particular purpose, and used for the communication</t>
+  </si>
+  <si>
+    <t>The capabilities supported on a  device, the standards to which the device conforms for a particular purpose, and used for the communication.</t>
+  </si>
+  <si>
+    <t>Device.specialization.id</t>
+  </si>
+  <si>
+    <t>Device.specialization.extension</t>
+  </si>
+  <si>
+    <t>Device.specialization.modifierExtension</t>
+  </si>
+  <si>
+    <t>Device.specialization.systemType</t>
+  </si>
+  <si>
+    <t>The standard that is used to operate and communicate</t>
+  </si>
+  <si>
+    <t>The standard that is used to operate and communicate.</t>
+  </si>
+  <si>
+    <t>Device.specialization.version</t>
+  </si>
+  <si>
+    <t>The version of the standard that is used to operate and communicate</t>
+  </si>
+  <si>
+    <t>The version of the standard that is used to operate and communicate.</t>
+  </si>
+  <si>
+    <t>Device.version</t>
+  </si>
+  <si>
+    <t>The actual design of the device or software version running on the device</t>
+  </si>
+  <si>
+    <t>The actual design of the device or software version running on the device.</t>
+  </si>
+  <si>
+    <t>Device.version.id</t>
+  </si>
+  <si>
+    <t>Device.version.extension</t>
+  </si>
+  <si>
+    <t>Device.version.modifierExtension</t>
+  </si>
+  <si>
+    <t>Device.version.type</t>
+  </si>
+  <si>
+    <t>The type of the device version</t>
+  </si>
+  <si>
+    <t>The type of the device version.</t>
+  </si>
+  <si>
+    <t>Device.version.component</t>
+  </si>
+  <si>
+    <t>A single component of the device version</t>
+  </si>
+  <si>
+    <t>A single component of the device version.</t>
+  </si>
+  <si>
+    <t>Device.version.value</t>
+  </si>
+  <si>
+    <t>The version text</t>
+  </si>
+  <si>
+    <t>The version text.</t>
+  </si>
+  <si>
+    <t>Device.property</t>
+  </si>
+  <si>
+    <t>The actual configuration settings of a device as it actually operates, e.g., regulation status, time properties</t>
+  </si>
+  <si>
+    <t>The actual configuration settings of a device as it actually operates, e.g., regulation status, time properties.</t>
+  </si>
+  <si>
+    <t>Device.property.id</t>
+  </si>
+  <si>
+    <t>Device.property.extension</t>
+  </si>
+  <si>
+    <t>Device.property.modifierExtension</t>
+  </si>
+  <si>
+    <t>Device.property.type</t>
+  </si>
+  <si>
+    <t>Code that specifies the property DeviceDefinitionPropetyCode (Extensible)</t>
+  </si>
+  <si>
+    <t>Code that specifies the property DeviceDefinitionPropetyCode (Extensible).</t>
+  </si>
+  <si>
+    <t>Device.property.valueQuantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>Property value as a quantity</t>
+  </si>
+  <si>
+    <t>Property value as a quantity.</t>
+  </si>
+  <si>
+    <t>Device.property.valueCode</t>
+  </si>
+  <si>
+    <t>Property value as a code, e.g., NTP4 (synced to NTP)</t>
+  </si>
+  <si>
+    <t>Property value as a code, e.g., NTP4 (synced to NTP).</t>
+  </si>
+  <si>
+    <t>Device.patient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Patient to whom Device is affixed</t>
+  </si>
+  <si>
+    <t>Patient information, If the device is affixed to a person.</t>
+  </si>
+  <si>
+    <t>If the device is implanted in a patient, then need to associate the device to the patient.</t>
+  </si>
+  <si>
+    <t>Device.owner</t>
+  </si>
+  <si>
+    <t>Organization responsible for device</t>
+  </si>
+  <si>
+    <t>An organization that is responsible for the provision and ongoing maintenance of the device.</t>
+  </si>
+  <si>
+    <t>Device.contact</t>
+  </si>
+  <si>
+    <t>Details for human/organization for support</t>
+  </si>
+  <si>
+    <t>Contact details for an organization or a particular human that is responsible for the device.</t>
+  </si>
+  <si>
+    <t>used for troubleshooting etc.</t>
+  </si>
+  <si>
+    <t>Device.location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Location|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Where the device is found</t>
+  </si>
+  <si>
+    <t>The place where the device can be found.</t>
+  </si>
+  <si>
+    <t>Device.location can be used to track device location.</t>
+  </si>
+  <si>
+    <t>Device.url</t>
+  </si>
+  <si>
+    <t>Network address to contact device</t>
+  </si>
+  <si>
+    <t>A network address on which the device may be contacted directly.</t>
+  </si>
+  <si>
+    <t>If the device is running a FHIR server, the network address should  be the Base URL from which a conformance statement may be retrieved.</t>
+  </si>
+  <si>
+    <t>Device.note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annotation
+</t>
+  </si>
+  <si>
+    <t>Device notes and comments</t>
+  </si>
+  <si>
+    <t>Descriptive information, usage information or implantation information that is not captured in an existing element.</t>
+  </si>
+  <si>
+    <t>Device.safety</t>
+  </si>
+  <si>
+    <t>Safety Characteristics of Device</t>
+  </si>
+  <si>
+    <t>Provides additional safety characteristics about a medical device.  For example devices containing latex.</t>
+  </si>
+  <si>
+    <t>Device.parent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Device|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>The parent device</t>
+  </si>
+  <si>
+    <t>The parent device.</t>
   </si>
 </sst>
 </file>
@@ -1609,7 +2226,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1786,6 +2403,170 @@
         <v>38</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B30" s="2"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -1793,14 +2574,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK76"/>
+  <dimension ref="A1:AK142"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.92578125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="22.04296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="34.765625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="33.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="12.94921875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="34.21875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="34.25390625" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="4.65625" customWidth="true" bestFit="true"/>
@@ -9843,6 +10624,6878 @@
         <v>96</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="D77" s="2"/>
+      <c r="E77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F77" s="2"/>
+      <c r="G77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" s="2"/>
+      <c r="Q77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R77" s="2"/>
+      <c r="S77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="D78" s="2"/>
+      <c r="E78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F78" s="2"/>
+      <c r="G78" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="P78" s="2"/>
+      <c r="Q78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R78" s="2"/>
+      <c r="S78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="D79" s="2"/>
+      <c r="E79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F79" s="2"/>
+      <c r="G79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" s="2"/>
+      <c r="Q79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R79" s="2"/>
+      <c r="S79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C80" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="D80" s="2"/>
+      <c r="E80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F80" s="2"/>
+      <c r="G80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="P80" s="2"/>
+      <c r="Q80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R80" s="2"/>
+      <c r="S80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="D81" s="2"/>
+      <c r="E81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F81" s="2"/>
+      <c r="G81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="P81" s="2"/>
+      <c r="Q81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R81" s="2"/>
+      <c r="S81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="D82" s="2"/>
+      <c r="E82" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="F82" s="2"/>
+      <c r="G82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="P82" s="2"/>
+      <c r="Q82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R82" s="2"/>
+      <c r="S82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="D83" s="2"/>
+      <c r="E83" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="F83" s="2"/>
+      <c r="G83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="P83" s="2"/>
+      <c r="Q83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R83" s="2"/>
+      <c r="S83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C84" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="D84" s="2"/>
+      <c r="E84" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F84" s="2"/>
+      <c r="G84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P84" s="2"/>
+      <c r="Q84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R84" s="2"/>
+      <c r="S84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C85" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="D85" s="2"/>
+      <c r="E85" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F85" s="2"/>
+      <c r="G85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="Q85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R85" s="2"/>
+      <c r="S85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C86" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="D86" s="2"/>
+      <c r="E86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F86" s="2"/>
+      <c r="G86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="P86" s="2"/>
+      <c r="Q86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R86" s="2"/>
+      <c r="S86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="D87" s="2"/>
+      <c r="E87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F87" s="2"/>
+      <c r="G87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="O87" s="2"/>
+      <c r="P87" s="2"/>
+      <c r="Q87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R87" s="2"/>
+      <c r="S87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="C88" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="D88" s="2"/>
+      <c r="E88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F88" s="2"/>
+      <c r="G88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="P88" s="2"/>
+      <c r="Q88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R88" s="2"/>
+      <c r="S88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C89" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="D89" s="2"/>
+      <c r="E89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F89" s="2"/>
+      <c r="G89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O89" s="2"/>
+      <c r="P89" s="2"/>
+      <c r="Q89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R89" s="2"/>
+      <c r="S89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C90" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="D90" s="2"/>
+      <c r="E90" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F90" s="2"/>
+      <c r="G90" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P90" s="2"/>
+      <c r="Q90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R90" s="2"/>
+      <c r="S90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="D91" s="2"/>
+      <c r="E91" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="F91" s="2"/>
+      <c r="G91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="Q91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R91" s="2"/>
+      <c r="S91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C92" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="D92" s="2"/>
+      <c r="E92" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="F92" s="2"/>
+      <c r="G92" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="O92" s="2"/>
+      <c r="P92" s="2"/>
+      <c r="Q92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R92" s="2"/>
+      <c r="S92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="C93" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="D93" s="2"/>
+      <c r="E93" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="F93" s="2"/>
+      <c r="G93" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="O93" s="2"/>
+      <c r="P93" s="2"/>
+      <c r="Q93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R93" s="2"/>
+      <c r="S93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="C94" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="D94" s="2"/>
+      <c r="E94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F94" s="2"/>
+      <c r="G94" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="Q94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R94" s="2"/>
+      <c r="S94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="D95" s="2"/>
+      <c r="E95" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="F95" s="2"/>
+      <c r="G95" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="P95" s="2"/>
+      <c r="Q95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R95" s="2"/>
+      <c r="S95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="D96" s="2"/>
+      <c r="E96" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="F96" s="2"/>
+      <c r="G96" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="P96" s="2"/>
+      <c r="Q96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R96" s="2"/>
+      <c r="S96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="D97" s="2"/>
+      <c r="E97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F97" s="2"/>
+      <c r="G97" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="Q97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R97" s="2"/>
+      <c r="S97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="D98" s="2"/>
+      <c r="E98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F98" s="2"/>
+      <c r="G98" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="P98" s="2"/>
+      <c r="Q98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R98" s="2"/>
+      <c r="S98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="C99" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="D99" s="2"/>
+      <c r="E99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F99" s="2"/>
+      <c r="G99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="O99" s="2"/>
+      <c r="P99" s="2"/>
+      <c r="Q99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R99" s="2"/>
+      <c r="S99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="C100" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="D100" s="2"/>
+      <c r="E100" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="F100" s="2"/>
+      <c r="G100" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="P100" s="2"/>
+      <c r="Q100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R100" s="2"/>
+      <c r="S100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="C101" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="D101" s="2"/>
+      <c r="E101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F101" s="2"/>
+      <c r="G101" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="O101" s="2"/>
+      <c r="P101" s="2"/>
+      <c r="Q101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R101" s="2"/>
+      <c r="S101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="C102" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="D102" s="2"/>
+      <c r="E102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F102" s="2"/>
+      <c r="G102" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="O102" s="2"/>
+      <c r="P102" s="2"/>
+      <c r="Q102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R102" s="2"/>
+      <c r="S102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C103" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="D103" s="2"/>
+      <c r="E103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F103" s="2"/>
+      <c r="G103" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="O103" s="2"/>
+      <c r="P103" s="2"/>
+      <c r="Q103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R103" s="2"/>
+      <c r="S103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="C104" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="D104" s="2"/>
+      <c r="E104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F104" s="2"/>
+      <c r="G104" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="O104" s="2"/>
+      <c r="P104" s="2"/>
+      <c r="Q104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R104" s="2"/>
+      <c r="S104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="C105" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="D105" s="2"/>
+      <c r="E105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F105" s="2"/>
+      <c r="G105" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="P105" s="2"/>
+      <c r="Q105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R105" s="2"/>
+      <c r="S105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C106" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="D106" s="2"/>
+      <c r="E106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F106" s="2"/>
+      <c r="G106" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="O106" s="2"/>
+      <c r="P106" s="2"/>
+      <c r="Q106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R106" s="2"/>
+      <c r="S106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="C107" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="D107" s="2"/>
+      <c r="E107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F107" s="2"/>
+      <c r="G107" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O107" s="2"/>
+      <c r="P107" s="2"/>
+      <c r="Q107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R107" s="2"/>
+      <c r="S107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="C108" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="D108" s="2"/>
+      <c r="E108" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F108" s="2"/>
+      <c r="G108" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P108" s="2"/>
+      <c r="Q108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R108" s="2"/>
+      <c r="S108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="C109" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="D109" s="2"/>
+      <c r="E109" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="F109" s="2"/>
+      <c r="G109" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="Q109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R109" s="2"/>
+      <c r="S109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C110" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="D110" s="2"/>
+      <c r="E110" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="F110" s="2"/>
+      <c r="G110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="O110" s="2"/>
+      <c r="P110" s="2"/>
+      <c r="Q110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R110" s="2"/>
+      <c r="S110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="D111" s="2"/>
+      <c r="E111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F111" s="2"/>
+      <c r="G111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="O111" s="2"/>
+      <c r="P111" s="2"/>
+      <c r="Q111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R111" s="2"/>
+      <c r="S111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="C112" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="D112" s="2"/>
+      <c r="E112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F112" s="2"/>
+      <c r="G112" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="O112" s="2"/>
+      <c r="P112" s="2"/>
+      <c r="Q112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R112" s="2"/>
+      <c r="S112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="C113" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="D113" s="2"/>
+      <c r="E113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F113" s="2"/>
+      <c r="G113" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="P113" s="2"/>
+      <c r="Q113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R113" s="2"/>
+      <c r="S113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="C114" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="D114" s="2"/>
+      <c r="E114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F114" s="2"/>
+      <c r="G114" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="O114" s="2"/>
+      <c r="P114" s="2"/>
+      <c r="Q114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R114" s="2"/>
+      <c r="S114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C115" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="D115" s="2"/>
+      <c r="E115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F115" s="2"/>
+      <c r="G115" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="O115" s="2"/>
+      <c r="P115" s="2"/>
+      <c r="Q115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R115" s="2"/>
+      <c r="S115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="D116" s="2"/>
+      <c r="E116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F116" s="2"/>
+      <c r="G116" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O116" s="2"/>
+      <c r="P116" s="2"/>
+      <c r="Q116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R116" s="2"/>
+      <c r="S116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="D117" s="2"/>
+      <c r="E117" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F117" s="2"/>
+      <c r="G117" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P117" s="2"/>
+      <c r="Q117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R117" s="2"/>
+      <c r="S117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="D118" s="2"/>
+      <c r="E118" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="F118" s="2"/>
+      <c r="G118" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P118" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="Q118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R118" s="2"/>
+      <c r="S118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="D119" s="2"/>
+      <c r="E119" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="F119" s="2"/>
+      <c r="G119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="O119" s="2"/>
+      <c r="P119" s="2"/>
+      <c r="Q119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R119" s="2"/>
+      <c r="S119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="C120" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="D120" s="2"/>
+      <c r="E120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F120" s="2"/>
+      <c r="G120" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="O120" s="2"/>
+      <c r="P120" s="2"/>
+      <c r="Q120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R120" s="2"/>
+      <c r="S120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="C121" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="D121" s="2"/>
+      <c r="E121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F121" s="2"/>
+      <c r="G121" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="O121" s="2"/>
+      <c r="P121" s="2"/>
+      <c r="Q121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R121" s="2"/>
+      <c r="S121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C122" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="D122" s="2"/>
+      <c r="E122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F122" s="2"/>
+      <c r="G122" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O122" s="2"/>
+      <c r="P122" s="2"/>
+      <c r="Q122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R122" s="2"/>
+      <c r="S122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="D123" s="2"/>
+      <c r="E123" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F123" s="2"/>
+      <c r="G123" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P123" s="2"/>
+      <c r="Q123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R123" s="2"/>
+      <c r="S123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="D124" s="2"/>
+      <c r="E124" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="F124" s="2"/>
+      <c r="G124" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P124" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="Q124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R124" s="2"/>
+      <c r="S124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="C125" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="D125" s="2"/>
+      <c r="E125" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="F125" s="2"/>
+      <c r="G125" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="O125" s="2"/>
+      <c r="P125" s="2"/>
+      <c r="Q125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R125" s="2"/>
+      <c r="S125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="C126" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="D126" s="2"/>
+      <c r="E126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F126" s="2"/>
+      <c r="G126" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="O126" s="2"/>
+      <c r="P126" s="2"/>
+      <c r="Q126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R126" s="2"/>
+      <c r="S126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="C127" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="D127" s="2"/>
+      <c r="E127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F127" s="2"/>
+      <c r="G127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="O127" s="2"/>
+      <c r="P127" s="2"/>
+      <c r="Q127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R127" s="2"/>
+      <c r="S127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="C128" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="D128" s="2"/>
+      <c r="E128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F128" s="2"/>
+      <c r="G128" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="O128" s="2"/>
+      <c r="P128" s="2"/>
+      <c r="Q128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R128" s="2"/>
+      <c r="S128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="C129" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="D129" s="2"/>
+      <c r="E129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F129" s="2"/>
+      <c r="G129" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O129" s="2"/>
+      <c r="P129" s="2"/>
+      <c r="Q129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R129" s="2"/>
+      <c r="S129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="C130" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="D130" s="2"/>
+      <c r="E130" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F130" s="2"/>
+      <c r="G130" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P130" s="2"/>
+      <c r="Q130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R130" s="2"/>
+      <c r="S130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="C131" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="D131" s="2"/>
+      <c r="E131" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="F131" s="2"/>
+      <c r="G131" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="O131" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P131" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="Q131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R131" s="2"/>
+      <c r="S131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="C132" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="D132" s="2"/>
+      <c r="E132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F132" s="2"/>
+      <c r="G132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="O132" s="2"/>
+      <c r="P132" s="2"/>
+      <c r="Q132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R132" s="2"/>
+      <c r="S132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="C133" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="D133" s="2"/>
+      <c r="E133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F133" s="2"/>
+      <c r="G133" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="O133" s="2"/>
+      <c r="P133" s="2"/>
+      <c r="Q133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R133" s="2"/>
+      <c r="S133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="C134" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="D134" s="2"/>
+      <c r="E134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F134" s="2"/>
+      <c r="G134" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="O134" s="2"/>
+      <c r="P134" s="2"/>
+      <c r="Q134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R134" s="2"/>
+      <c r="S134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="C135" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="D135" s="2"/>
+      <c r="E135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F135" s="2"/>
+      <c r="G135" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="Q135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R135" s="2"/>
+      <c r="S135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="C136" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="D136" s="2"/>
+      <c r="E136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F136" s="2"/>
+      <c r="G136" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="O136" s="2"/>
+      <c r="P136" s="2"/>
+      <c r="Q136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R136" s="2"/>
+      <c r="S136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="C137" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="D137" s="2"/>
+      <c r="E137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F137" s="2"/>
+      <c r="G137" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="O137" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="P137" s="2"/>
+      <c r="Q137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R137" s="2"/>
+      <c r="S137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="C138" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="D138" s="2"/>
+      <c r="E138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F138" s="2"/>
+      <c r="G138" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="O138" s="2"/>
+      <c r="P138" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="Q138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R138" s="2"/>
+      <c r="S138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK138" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="C139" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="D139" s="2"/>
+      <c r="E139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F139" s="2"/>
+      <c r="G139" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="O139" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="P139" s="2"/>
+      <c r="Q139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R139" s="2"/>
+      <c r="S139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK139" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="C140" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="D140" s="2"/>
+      <c r="E140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F140" s="2"/>
+      <c r="G140" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="O140" s="2"/>
+      <c r="P140" s="2"/>
+      <c r="Q140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R140" s="2"/>
+      <c r="S140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK140" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="C141" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="D141" s="2"/>
+      <c r="E141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F141" s="2"/>
+      <c r="G141" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K141" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M141" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="O141" s="2"/>
+      <c r="P141" s="2"/>
+      <c r="Q141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R141" s="2"/>
+      <c r="S141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG141" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AH141" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK141" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="C142" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="D142" s="2"/>
+      <c r="E142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F142" s="2"/>
+      <c r="G142" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L142" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="O142" s="2"/>
+      <c r="P142" s="2"/>
+      <c r="Q142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R142" s="2"/>
+      <c r="S142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK142" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -1490,7 +1490,7 @@
     <t>Stockholm Device</t>
   </si>
   <si>
-    <t>2026-10-29T10:49:58+00:00</t>
+    <t>2026-10-29T11:54:13+00:00</t>
   </si>
   <si>
     <t>Profile for devices and software systems used in genomic workflows, including sequencing platforms and bioinformatics pipelines referenced by procedures and analyses.</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -1490,7 +1490,7 @@
     <t>Stockholm Device</t>
   </si>
   <si>
-    <t>2026-10-29T11:54:13+00:00</t>
+    <t>2026-10-29T12:12:40+00:00</t>
   </si>
   <si>
     <t>Profile for devices and software systems used in genomic workflows, including sequencing platforms and bioinformatics pipelines referenced by procedures and analyses.</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -1490,7 +1490,7 @@
     <t>Stockholm Device</t>
   </si>
   <si>
-    <t>2026-10-29T12:12:40+00:00</t>
+    <t>2026-10-29T12:15:14+00:00</t>
   </si>
   <si>
     <t>Profile for devices and software systems used in genomic workflows, including sequencing platforms and bioinformatics pipelines referenced by procedures and analyses.</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -1490,7 +1490,7 @@
     <t>Stockholm Device</t>
   </si>
   <si>
-    <t>2026-10-29T12:15:14+00:00</t>
+    <t>2026-10-29T12:17:57+00:00</t>
   </si>
   <si>
     <t>Profile for devices and software systems used in genomic workflows, including sequencing platforms and bioinformatics pipelines referenced by procedures and analyses.</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -1490,7 +1490,7 @@
     <t>Stockholm Device</t>
   </si>
   <si>
-    <t>2026-10-29T12:17:57+00:00</t>
+    <t>2026-10-29T12:25:30+00:00</t>
   </si>
   <si>
     <t>Profile for devices and software systems used in genomic workflows, including sequencing platforms and bioinformatics pipelines referenced by procedures and analyses.</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -1490,7 +1490,7 @@
     <t>Stockholm Device</t>
   </si>
   <si>
-    <t>2026-10-29T12:25:30+00:00</t>
+    <t>2026-10-29T12:29:08+00:00</t>
   </si>
   <si>
     <t>Profile for devices and software systems used in genomic workflows, including sequencing platforms and bioinformatics pipelines referenced by procedures and analyses.</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4788" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6592" uniqueCount="682">
   <si>
     <t>Property</t>
   </si>
@@ -1490,7 +1490,7 @@
     <t>Stockholm Device</t>
   </si>
   <si>
-    <t>2026-10-29T12:29:08+00:00</t>
+    <t>2026-10-29T12:36:03+00:00</t>
   </si>
   <si>
     <t>Profile for devices and software systems used in genomic workflows, including sequencing platforms and bioinformatics pipelines referenced by procedures and analyses.</t>
@@ -2093,6 +2093,54 @@
   </si>
   <si>
     <t>The parent device.</t>
+  </si>
+  <si>
+    <t>stockholm-genomic-patient</t>
+  </si>
+  <si>
+    <t>https://pub.regionstockholm.se/fhir/ImplementationGuide/Testmall/StructureDefinition/stockholm-genomic-patient</t>
+  </si>
+  <si>
+    <t>StockholmGenomicPatient</t>
+  </si>
+  <si>
+    <t>Stockholm Genomic Patient</t>
+  </si>
+  <si>
+    <t>Minimal Patient profile for genomic studies. Exposes only the key elements required: identifier, gender, birthDate and deceased.</t>
+  </si>
+  <si>
+    <t>Minimal patient profile for genomic studies</t>
+  </si>
+  <si>
+    <t>Patient identifiers used in genomic workflows</t>
+  </si>
+  <si>
+    <t>Identifiers required to safely link genomic case resources to the correct patient context.</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>A name associated with the patient</t>
+  </si>
+  <si>
+    <t>Administrative gender</t>
+  </si>
+  <si>
+    <t>Administrative gender recorded for the patient according to FHIR core semantics.</t>
+  </si>
+  <si>
+    <t>Date of birth</t>
+  </si>
+  <si>
+    <t>Birth date used for patient identification and genomic interpretation context.</t>
+  </si>
+  <si>
+    <t>Deceased indicator or date</t>
+  </si>
+  <si>
+    <t>States whether the patient is deceased, optionally with date/time where available.</t>
   </si>
 </sst>
 </file>
@@ -2226,7 +2274,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -2567,6 +2615,170 @@
         <v>38</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B51" s="2"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B58" s="2"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -2574,10 +2786,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK142"/>
+  <dimension ref="A1:AK195"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="22.04296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="22.47265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="34.765625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="33.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="12.94921875" customWidth="true" bestFit="true" hidden="true"/>
@@ -17496,6 +17708,5601 @@
         <v>96</v>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="C143" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D143" s="2"/>
+      <c r="E143" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F143" s="2"/>
+      <c r="G143" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="M143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="O143" s="2"/>
+      <c r="P143" s="2"/>
+      <c r="Q143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R143" s="2"/>
+      <c r="S143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG143" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="AH143" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK143" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="C144" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="D144" s="2"/>
+      <c r="E144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F144" s="2"/>
+      <c r="G144" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K144" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="P144" s="2"/>
+      <c r="Q144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R144" s="2"/>
+      <c r="S144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG144" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH144" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK144" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="C145" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="D145" s="2"/>
+      <c r="E145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F145" s="2"/>
+      <c r="G145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O145" s="2"/>
+      <c r="P145" s="2"/>
+      <c r="Q145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R145" s="2"/>
+      <c r="S145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="C146" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="D146" s="2"/>
+      <c r="E146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F146" s="2"/>
+      <c r="G146" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J146" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K146" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="N146" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="O146" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="P146" s="2"/>
+      <c r="Q146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R146" s="2"/>
+      <c r="S146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK146" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C147" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="D147" s="2"/>
+      <c r="E147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F147" s="2"/>
+      <c r="G147" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="O147" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="P147" s="2"/>
+      <c r="Q147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R147" s="2"/>
+      <c r="S147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG147" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK147" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C148" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="D148" s="2"/>
+      <c r="E148" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="F148" s="2"/>
+      <c r="G148" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L148" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="O148" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="P148" s="2"/>
+      <c r="Q148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R148" s="2"/>
+      <c r="S148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG148" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AH148" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK148" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="C149" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="D149" s="2"/>
+      <c r="E149" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="F149" s="2"/>
+      <c r="G149" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H149" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="O149" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="P149" s="2"/>
+      <c r="Q149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R149" s="2"/>
+      <c r="S149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG149" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AH149" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI149" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK149" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="C150" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="D150" s="2"/>
+      <c r="E150" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F150" s="2"/>
+      <c r="G150" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H150" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L150" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M150" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="O150" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P150" s="2"/>
+      <c r="Q150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R150" s="2"/>
+      <c r="S150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG150" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AH150" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI150" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK150" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="C151" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="D151" s="2"/>
+      <c r="E151" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F151" s="2"/>
+      <c r="G151" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H151" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J151" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L151" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O151" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P151" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="Q151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R151" s="2"/>
+      <c r="S151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG151" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AH151" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI151" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK151" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="C152" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="D152" s="2"/>
+      <c r="E152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F152" s="2"/>
+      <c r="G152" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I152" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K152" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L152" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="O152" s="2"/>
+      <c r="P152" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="Q152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R152" s="2"/>
+      <c r="S152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG152" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AH152" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK152" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="C153" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="D153" s="2"/>
+      <c r="E153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F153" s="2"/>
+      <c r="G153" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L153" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O153" s="2"/>
+      <c r="P153" s="2"/>
+      <c r="Q153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R153" s="2"/>
+      <c r="S153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG153" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AH153" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK153" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="C154" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="D154" s="2"/>
+      <c r="E154" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F154" s="2"/>
+      <c r="G154" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H154" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L154" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M154" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O154" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P154" s="2"/>
+      <c r="Q154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R154" s="2"/>
+      <c r="S154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AD154" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AE154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF154" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AG154" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AH154" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI154" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK154" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="C155" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D155" s="2"/>
+      <c r="E155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F155" s="2"/>
+      <c r="G155" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J155" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K155" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L155" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M155" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="P155" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="Q155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R155" s="2"/>
+      <c r="S155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y155" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="Z155" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AA155" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AB155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG155" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AH155" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK155" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="C156" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="D156" s="2"/>
+      <c r="E156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F156" s="2"/>
+      <c r="G156" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I156" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K156" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L156" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M156" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="O156" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="P156" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Q156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R156" s="2"/>
+      <c r="S156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Z156" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AA156" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AB156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG156" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AH156" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK156" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C157" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="D157" s="2"/>
+      <c r="E157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F157" s="2"/>
+      <c r="G157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K157" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L157" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="M157" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="N157" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="O157" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="P157" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Q157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R157" s="2"/>
+      <c r="S157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U157" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="V157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG157" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AH157" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK157" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="C158" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="D158" s="2"/>
+      <c r="E158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F158" s="2"/>
+      <c r="G158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K158" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L158" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M158" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="P158" s="2"/>
+      <c r="Q158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R158" s="2"/>
+      <c r="S158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U158" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="V158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG158" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AH158" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK158" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="C159" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="D159" s="2"/>
+      <c r="E159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F159" s="2"/>
+      <c r="G159" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K159" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L159" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M159" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N159" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O159" s="2"/>
+      <c r="P159" s="2"/>
+      <c r="Q159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R159" s="2"/>
+      <c r="S159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG159" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AH159" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK159" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="C160" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="D160" s="2"/>
+      <c r="E160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F160" s="2"/>
+      <c r="G160" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K160" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L160" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M160" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="O160" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="P160" s="2"/>
+      <c r="Q160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R160" s="2"/>
+      <c r="S160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG160" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AH160" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK160" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="C161" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="D161" s="2"/>
+      <c r="E161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F161" s="2"/>
+      <c r="G161" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J161" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K161" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L161" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M161" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N161" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O161" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="P161" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="Q161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R161" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="S161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG161" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AH161" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK161" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C162" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D162" s="2"/>
+      <c r="E162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F162" s="2"/>
+      <c r="G162" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H162" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K162" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L162" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M162" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="N162" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="O162" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="P162" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="Q162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R162" s="2"/>
+      <c r="S162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG162" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AH162" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI162" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK162" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="C163" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="D163" s="2"/>
+      <c r="E163" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F163" s="2"/>
+      <c r="G163" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H163" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I163" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J163" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K163" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L163" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M163" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="N163" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="O163" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="P163" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="Q163" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R163" s="2"/>
+      <c r="S163" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T163" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U163" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V163" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W163" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X163" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y163" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z163" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA163" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB163" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC163" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD163" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE163" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF163" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG163" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AH163" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI163" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ163" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK163" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="C164" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="D164" s="2"/>
+      <c r="E164" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F164" s="2"/>
+      <c r="G164" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I164" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J164" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K164" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L164" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M164" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="P164" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="Q164" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R164" s="2"/>
+      <c r="S164" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T164" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U164" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V164" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W164" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X164" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y164" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="Z164" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AA164" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AB164" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC164" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD164" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE164" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF164" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG164" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AH164" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ164" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK164" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="C165" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="D165" s="2"/>
+      <c r="E165" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F165" s="2"/>
+      <c r="G165" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I165" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J165" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K165" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L165" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M165" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="N165" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="O165" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="P165" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="Q165" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R165" s="2"/>
+      <c r="S165" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T165" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U165" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V165" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W165" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X165" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y165" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z165" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA165" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB165" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC165" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD165" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE165" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF165" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG165" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AH165" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ165" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK165" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="C166" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="D166" s="2"/>
+      <c r="E166" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F166" s="2"/>
+      <c r="G166" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I166" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J166" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K166" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L166" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M166" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="N166" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="O166" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="P166" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Q166" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R166" s="2"/>
+      <c r="S166" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T166" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U166" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V166" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W166" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X166" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y166" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z166" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA166" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB166" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC166" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD166" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE166" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF166" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG166" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AH166" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ166" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK166" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="C167" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="D167" s="2"/>
+      <c r="E167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F167" s="2"/>
+      <c r="G167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H167" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K167" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L167" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M167" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="N167" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="O167" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="P167" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="Q167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R167" s="2"/>
+      <c r="S167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG167" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AH167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI167" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK167" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="C168" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="D168" s="2"/>
+      <c r="E168" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F168" s="2"/>
+      <c r="G168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I168" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J168" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K168" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L168" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M168" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O168" s="2"/>
+      <c r="P168" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="Q168" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R168" s="2"/>
+      <c r="S168" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T168" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U168" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V168" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W168" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X168" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y168" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Z168" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AA168" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AB168" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC168" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD168" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE168" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF168" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG168" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AH168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ168" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK168" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="C169" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="D169" s="2"/>
+      <c r="E169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F169" s="2"/>
+      <c r="G169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L169" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M169" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="N169" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="O169" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="P169" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="Q169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R169" s="2"/>
+      <c r="S169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG169" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AH169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK169" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="C170" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="D170" s="2"/>
+      <c r="E170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F170" s="2"/>
+      <c r="G170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H170" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L170" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M170" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="N170" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="O170" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="P170" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="Q170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R170" s="2"/>
+      <c r="S170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG170" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AH170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI170" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK170" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C171" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="D171" s="2"/>
+      <c r="E171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F171" s="2"/>
+      <c r="G171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H171" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L171" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M171" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="N171" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="O171" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="P171" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="Q171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R171" s="2"/>
+      <c r="S171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG171" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AH171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI171" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK171" t="s" s="2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C172" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="D172" s="2"/>
+      <c r="E172" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F172" s="2"/>
+      <c r="G172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I172" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J172" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K172" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L172" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M172" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N172" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O172" s="2"/>
+      <c r="P172" s="2"/>
+      <c r="Q172" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R172" s="2"/>
+      <c r="S172" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T172" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U172" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V172" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W172" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X172" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y172" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z172" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA172" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB172" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC172" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD172" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE172" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF172" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG172" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AH172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ172" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK172" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="C173" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="D173" s="2"/>
+      <c r="E173" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F173" s="2"/>
+      <c r="G173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H173" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I173" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J173" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K173" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L173" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M173" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O173" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P173" s="2"/>
+      <c r="Q173" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R173" s="2"/>
+      <c r="S173" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T173" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U173" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V173" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W173" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X173" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y173" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z173" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA173" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB173" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC173" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD173" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE173" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF173" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG173" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AH173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI173" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ173" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK173" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="C174" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="D174" s="2"/>
+      <c r="E174" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="F174" s="2"/>
+      <c r="G174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H174" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I174" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J174" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K174" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L174" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M174" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="O174" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P174" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="Q174" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R174" s="2"/>
+      <c r="S174" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T174" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U174" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V174" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W174" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X174" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y174" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z174" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA174" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB174" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC174" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD174" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE174" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF174" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG174" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AH174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI174" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ174" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK174" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="C175" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="D175" s="2"/>
+      <c r="E175" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F175" s="2"/>
+      <c r="G175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H175" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I175" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J175" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K175" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L175" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M175" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N175" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="O175" s="2"/>
+      <c r="P175" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="Q175" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R175" s="2"/>
+      <c r="S175" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T175" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U175" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V175" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W175" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X175" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y175" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Z175" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AA175" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AB175" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC175" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD175" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE175" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF175" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG175" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AH175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI175" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ175" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK175" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="C176" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="D176" s="2"/>
+      <c r="E176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F176" s="2"/>
+      <c r="G176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H176" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L176" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M176" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="N176" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="O176" s="2"/>
+      <c r="P176" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="Q176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R176" s="2"/>
+      <c r="S176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG176" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AH176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI176" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK176" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="C177" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="D177" s="2"/>
+      <c r="E177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F177" s="2"/>
+      <c r="G177" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H177" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L177" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M177" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N177" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="O177" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="P177" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="Q177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R177" s="2"/>
+      <c r="S177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG177" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AH177" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI177" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK177" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B178" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="C178" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="D178" s="2"/>
+      <c r="E178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F178" s="2"/>
+      <c r="G178" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H178" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L178" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M178" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="N178" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="O178" s="2"/>
+      <c r="P178" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="Q178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R178" s="2"/>
+      <c r="S178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG178" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AH178" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI178" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK178" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="C179" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="D179" s="2"/>
+      <c r="E179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F179" s="2"/>
+      <c r="G179" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H179" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L179" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M179" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N179" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="O179" s="2"/>
+      <c r="P179" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="Q179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R179" s="2"/>
+      <c r="S179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y179" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="Z179" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AA179" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AB179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG179" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AH179" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI179" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK179" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="C180" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="D180" s="2"/>
+      <c r="E180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F180" s="2"/>
+      <c r="G180" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H180" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L180" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M180" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="N180" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="O180" s="2"/>
+      <c r="P180" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Q180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R180" s="2"/>
+      <c r="S180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG180" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AH180" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI180" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ180" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AK180" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="C181" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="D181" s="2"/>
+      <c r="E181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F181" s="2"/>
+      <c r="G181" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H181" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L181" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M181" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="N181" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="O181" s="2"/>
+      <c r="P181" s="2"/>
+      <c r="Q181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R181" s="2"/>
+      <c r="S181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG181" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AH181" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI181" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK181" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B182" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="C182" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="D182" s="2"/>
+      <c r="E182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F182" s="2"/>
+      <c r="G182" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H182" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L182" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M182" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="O182" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="P182" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="Q182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R182" s="2"/>
+      <c r="S182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG182" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AH182" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI182" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK182" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B183" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="C183" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="D183" s="2"/>
+      <c r="E183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F183" s="2"/>
+      <c r="G183" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H183" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L183" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M183" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N183" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O183" s="2"/>
+      <c r="P183" s="2"/>
+      <c r="Q183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R183" s="2"/>
+      <c r="S183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG183" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AH183" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI183" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK183" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B184" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="C184" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="D184" s="2"/>
+      <c r="E184" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F184" s="2"/>
+      <c r="G184" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L184" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M184" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N184" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O184" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P184" s="2"/>
+      <c r="Q184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R184" s="2"/>
+      <c r="S184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG184" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AH184" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK184" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B185" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="C185" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="D185" s="2"/>
+      <c r="E185" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="F185" s="2"/>
+      <c r="G185" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J185" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K185" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L185" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M185" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N185" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="O185" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P185" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="Q185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R185" s="2"/>
+      <c r="S185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG185" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AH185" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK185" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C186" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="D186" s="2"/>
+      <c r="E186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F186" s="2"/>
+      <c r="G186" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H186" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L186" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M186" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="N186" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="O186" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="P186" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="Q186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R186" s="2"/>
+      <c r="S186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y186" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="Z186" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AA186" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AB186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG186" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AH186" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI186" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK186" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="C187" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="D187" s="2"/>
+      <c r="E187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F187" s="2"/>
+      <c r="G187" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H187" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L187" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M187" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="N187" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="O187" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="P187" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="Q187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R187" s="2"/>
+      <c r="S187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG187" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AH187" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI187" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK187" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B188" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C188" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="D188" s="2"/>
+      <c r="E188" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="F188" s="2"/>
+      <c r="G188" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I188" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J188" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K188" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L188" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M188" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="N188" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="O188" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="P188" s="2"/>
+      <c r="Q188" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R188" s="2"/>
+      <c r="S188" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T188" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U188" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V188" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W188" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X188" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y188" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z188" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA188" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB188" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC188" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD188" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE188" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF188" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG188" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AH188" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ188" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK188" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C189" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="D189" s="2"/>
+      <c r="E189" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F189" s="2"/>
+      <c r="G189" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H189" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I189" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J189" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K189" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L189" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M189" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="N189" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="O189" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="P189" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="Q189" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R189" s="2"/>
+      <c r="S189" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T189" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U189" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V189" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W189" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X189" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y189" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z189" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA189" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB189" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC189" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD189" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE189" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF189" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG189" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AH189" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI189" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ189" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK189" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B190" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C190" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="D190" s="2"/>
+      <c r="E190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F190" s="2"/>
+      <c r="G190" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J190" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K190" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L190" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M190" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="N190" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="O190" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="P190" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="Q190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R190" s="2"/>
+      <c r="S190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG190" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AH190" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK190" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B191" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C191" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="D191" s="2"/>
+      <c r="E191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F191" s="2"/>
+      <c r="G191" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H191" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L191" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M191" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N191" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O191" s="2"/>
+      <c r="P191" s="2"/>
+      <c r="Q191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R191" s="2"/>
+      <c r="S191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG191" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AH191" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI191" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK191" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B192" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="C192" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="D192" s="2"/>
+      <c r="E192" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F192" s="2"/>
+      <c r="G192" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L192" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M192" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N192" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O192" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P192" s="2"/>
+      <c r="Q192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R192" s="2"/>
+      <c r="S192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG192" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AH192" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK192" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B193" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C193" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="D193" s="2"/>
+      <c r="E193" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="F193" s="2"/>
+      <c r="G193" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I193" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J193" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K193" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L193" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M193" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N193" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="O193" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P193" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="Q193" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R193" s="2"/>
+      <c r="S193" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T193" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U193" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V193" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W193" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X193" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y193" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z193" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA193" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB193" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC193" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD193" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE193" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF193" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG193" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AH193" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ193" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK193" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B194" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="C194" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="D194" s="2"/>
+      <c r="E194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F194" s="2"/>
+      <c r="G194" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H194" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K194" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L194" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M194" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="O194" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="P194" s="2"/>
+      <c r="Q194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R194" s="2"/>
+      <c r="S194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG194" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AH194" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI194" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK194" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B195" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C195" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="D195" s="2"/>
+      <c r="E195" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F195" s="2"/>
+      <c r="G195" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H195" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I195" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J195" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K195" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L195" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M195" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="N195" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="O195" s="2"/>
+      <c r="P195" s="2"/>
+      <c r="Q195" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R195" s="2"/>
+      <c r="S195" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T195" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U195" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V195" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W195" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X195" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y195" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="Z195" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AA195" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AB195" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC195" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD195" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE195" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF195" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG195" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AH195" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI195" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ195" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK195" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -1490,7 +1490,7 @@
     <t>Stockholm Device</t>
   </si>
   <si>
-    <t>2026-10-29T12:36:03+00:00</t>
+    <t>2026-10-29T12:50:53+00:00</t>
   </si>
   <si>
     <t>Profile for devices and software systems used in genomic workflows, including sequencing platforms and bioinformatics pipelines referenced by procedures and analyses.</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -1490,7 +1490,7 @@
     <t>Stockholm Device</t>
   </si>
   <si>
-    <t>2026-10-29T12:50:53+00:00</t>
+    <t>2026-10-29T13:31:58+00:00</t>
   </si>
   <si>
     <t>Profile for devices and software systems used in genomic workflows, including sequencing platforms and bioinformatics pipelines referenced by procedures and analyses.</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -1490,7 +1490,7 @@
     <t>Stockholm Device</t>
   </si>
   <si>
-    <t>2026-10-29T13:31:58+00:00</t>
+    <t>2026-10-29T13:46:42+00:00</t>
   </si>
   <si>
     <t>Profile for devices and software systems used in genomic workflows, including sequencing platforms and bioinformatics pipelines referenced by procedures and analyses.</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -1490,7 +1490,7 @@
     <t>Stockholm Device</t>
   </si>
   <si>
-    <t>2026-10-29T13:46:42+00:00</t>
+    <t>2026-10-29T13:53:27+00:00</t>
   </si>
   <si>
     <t>Profile for devices and software systems used in genomic workflows, including sequencing platforms and bioinformatics pipelines referenced by procedures and analyses.</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -1490,7 +1490,7 @@
     <t>Stockholm Device</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:27+00:00</t>
+    <t>2026-10-29T13:59:37+00:00</t>
   </si>
   <si>
     <t>Profile for devices and software systems used in genomic workflows, including sequencing platforms and bioinformatics pipelines referenced by procedures and analyses.</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -1490,7 +1490,7 @@
     <t>Stockholm Device</t>
   </si>
   <si>
-    <t>2026-10-29T13:59:37+00:00</t>
+    <t>2026-10-30T08:47:43+00:00</t>
   </si>
   <si>
     <t>Profile for devices and software systems used in genomic workflows, including sequencing platforms and bioinformatics pipelines referenced by procedures and analyses.</t>
